--- a/data/Курская_Контроль_Октябрь.xlsx
+++ b/data/Курская_Контроль_Октябрь.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Downloads\Курская\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548E2745-C774-4AEE-9E46-3501A01DA1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CA440F-48BA-4099-87D6-627F9B070CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4040,7 +4040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W119"/>
+  <dimension ref="A1:X119"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4060,9 +4060,10 @@
     <col min="21" max="21" width="34" customWidth="1"/>
     <col min="22" max="22" width="18" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="11.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18">
+    <row r="1" spans="1:24" ht="18">
       <c r="A1" s="33" t="s">
         <v>16</v>
       </c>
@@ -4087,7 +4088,7 @@
       <c r="T1" s="33"/>
       <c r="U1" s="33"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="34" t="s">
         <v>17</v>
       </c>
@@ -4112,7 +4113,7 @@
       <c r="T2" s="34"/>
       <c r="U2" s="34"/>
     </row>
-    <row r="3" spans="1:23" ht="36" customHeight="1">
+    <row r="3" spans="1:24" ht="36" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>18</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="20">
         <v>46296</v>
       </c>
@@ -4246,10 +4247,10 @@
       </c>
       <c r="W4" s="31">
         <f>SUM(G4:G34)+SUM(J4:J34)</f>
-        <v>453343</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
+        <v>473950</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" s="20">
         <v>46297</v>
       </c>
@@ -4314,10 +4315,14 @@
       </c>
       <c r="W5" s="31">
         <f>AVERAGE(G4:G34,J4:J34)</f>
-        <v>34872.538461538461</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+        <v>33853.571428571428</v>
+      </c>
+      <c r="X5" s="31">
+        <f>W5*31</f>
+        <v>1049460.7142857143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" s="20">
         <v>46298</v>
       </c>
@@ -4381,7 +4386,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="20">
         <v>46299</v>
       </c>
@@ -4445,7 +4450,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="20">
         <v>46300</v>
       </c>
@@ -4507,7 +4512,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="27.6">
+    <row r="9" spans="1:24" ht="27.6">
       <c r="A9" s="20">
         <v>46301</v>
       </c>
@@ -4573,7 +4578,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="20">
         <v>46302</v>
       </c>
@@ -4635,7 +4640,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="20">
         <v>46303</v>
       </c>
@@ -4703,7 +4708,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="27.6">
+    <row r="12" spans="1:24" ht="27.6">
       <c r="A12" s="20">
         <v>46304</v>
       </c>
@@ -4773,7 +4778,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="20">
         <v>46305</v>
       </c>
@@ -4837,7 +4842,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="27.6">
+    <row r="14" spans="1:24" ht="27.6">
       <c r="A14" s="20">
         <v>46306</v>
       </c>
@@ -4901,7 +4906,7 @@
         <v>✅ ОК</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="20">
         <v>46307</v>
       </c>
@@ -4959,11 +4964,11 @@
       </c>
       <c r="U15" s="10"/>
       <c r="V15" s="24" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR(A15="",C15="",R14=""),"",IF(D15=R14,"✅ ОК","⚠️ ПРОВЕРИТЬ"))</f>
         <v>⚠️ ПРОВЕРИТЬ</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24" ht="27.6">
       <c r="A16" s="20">
         <v>46308</v>
       </c>
@@ -5010,14 +5015,16 @@
         <f t="shared" si="4"/>
         <v>10375</v>
       </c>
-      <c r="R16" s="29"/>
-      <c r="S16" s="28" t="str">
+      <c r="R16" s="29">
+        <v>15925</v>
+      </c>
+      <c r="S16" s="28">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5550</v>
       </c>
       <c r="T16" s="9" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>⚠️ ИЗЛИШЕК 5550,0 ₽</v>
       </c>
       <c r="U16" s="10"/>
       <c r="V16" s="24" t="str">
@@ -5035,12 +5042,18 @@
       <c r="C17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="28" t="str">
+      <c r="D17" s="29">
+        <v>15925</v>
+      </c>
+      <c r="E17" s="29">
+        <v>0</v>
+      </c>
+      <c r="F17" s="29">
+        <v>20607</v>
+      </c>
+      <c r="G17" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>20607</v>
       </c>
       <c r="H17" s="29"/>
       <c r="I17" s="29"/>
@@ -5053,7 +5066,7 @@
       <c r="M17" s="29"/>
       <c r="N17" s="28">
         <f>IF(OR(C17="Ирина",C17="Обе"),Настройки!$B$3+IF(G17="",0,G17)*Настройки!$C$3,0)</f>
-        <v>3500</v>
+        <v>4530.3500000000004</v>
       </c>
       <c r="O17" s="28">
         <f>IF(OR(C17="Татьяна",C17="Обе"),Настройки!$B$4+IF(J17="",0,J17)*Настройки!$C$4,0)</f>
@@ -5062,21 +5075,23 @@
       <c r="P17" s="29"/>
       <c r="Q17" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="29"/>
-      <c r="S17" s="28" t="str">
+        <v>15925</v>
+      </c>
+      <c r="R17" s="29">
+        <v>15925</v>
+      </c>
+      <c r="S17" s="28">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T17" s="9" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>✅ ВСЁ ТОЧНО</v>
       </c>
       <c r="U17" s="10"/>
       <c r="V17" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>✅ ОК</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5089,7 +5104,9 @@
       <c r="C18" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="29"/>
+      <c r="D18" s="29">
+        <v>15925</v>
+      </c>
       <c r="E18" s="29"/>
       <c r="F18" s="29"/>
       <c r="G18" s="28" t="str">
@@ -5116,7 +5133,7 @@
       <c r="P18" s="29"/>
       <c r="Q18" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15925</v>
       </c>
       <c r="R18" s="29"/>
       <c r="S18" s="28" t="str">
@@ -5130,7 +5147,7 @@
       <c r="U18" s="10"/>
       <c r="V18" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>✅ ОК</v>
       </c>
     </row>
     <row r="19" spans="1:22">
